--- a/004/xy_004_data.xlsx
+++ b/004/xy_004_data.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>

--- a/004/xy_004_data.xlsx
+++ b/004/xy_004_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rockets and Feathers</t>
+          <t>Gasoline Is Mostly Crude Oil</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pump prices track crude on the way up and dawdle on the way down.</t>
+          <t>Pump prices track crude oil closely, month after month, not just over the decades.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 02:03</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 02:03</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C435"/>
+  <dimension ref="A1:C434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5577,17 +5577,6 @@
       </c>
       <c r="C434" t="n">
         <v>4.058</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B435" t="n">
-        <v>98.41799999999999</v>
-      </c>
-      <c r="C435" t="n">
-        <v>4.318000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -87865,8 +87854,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="59" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="61" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -87909,7 +87898,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0320786, 0.588179</t>
+          <t>0.0320066, 0.590648</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -87930,14 +87919,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.000133288, 0.0475934, 0.253135</t>
+          <t>-0.000135115, 0.0477215, 0.251443</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9357</v>
+        <v>0.9362</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9354</v>
+        <v>0.9359</v>
       </c>
     </row>
     <row r="4">
@@ -87951,14 +87940,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.07124e-06, 7.3743e-05, 0.0361248, 0.41749</t>
+          <t>-1.02611e-06, 6.3245e-05, 0.0367324, 0.408921</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9365</v>
+        <v>0.9369</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9364</v>
       </c>
     </row>
     <row r="5">
@@ -87972,14 +87961,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.53811e-08, -5.3122e-06, 0.000468533, 0.0219326, 0.57437</t>
+          <t>1.75445e-08, -5.86232e-06, 0.000513275, 0.0205607, 0.587632</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9366</v>
+        <v>0.9371</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9365</v>
       </c>
     </row>
     <row r="6">
@@ -87996,7 +87985,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -88022,7 +88011,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.87720719354609e-243</v>
+        <v>6.224735018652152e-243</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -88035,7 +88024,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.982409487571158e-93</v>
+        <v>1.525241723054294e-93</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -88049,7 +88038,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>y = 0.0321x + 0.588</t>
+          <t>y = 0.032x + 0.591</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>

--- a/004/xy_004_data.xlsx
+++ b/004/xy_004_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>28/09/2026</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gasoline Is Mostly Crude Oil</t>
+          <t>Crude Oil vs Gasoline</t>
         </is>
       </c>
     </row>
@@ -488,293 +488,281 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pump prices track crude oil closely, month after month, not just over the decades.</t>
+          <t>Pump prices track crude oil month to month.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Crude oil explains over 90% of the variation in gasoline prices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>publication</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://xandyregression.substack.com</t>
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+    </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>X label</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>WTI crude ($/barrel, FRED)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X label</t>
+          <t>X detail</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WTI crude ($/barrel, FRED)</t>
+          <t>WTI crude oil spot price, $ per barrel, daily averaged to monthly, FRED DCOILWTICO, 08/1990 - present</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X detail</t>
+          <t>X source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WTI crude oil spot price, $ per barrel, daily averaged to monthly, FRED DCOILWTICO, 08/1990 - present</t>
+          <t>FRED DCOILWTICO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X source</t>
+          <t>X source URL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FRED DCOILWTICO</t>
+          <t>https://fred.stlouisfed.org/series/DCOILWTICO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X source URL</t>
+          <t>X licence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://fred.stlouisfed.org/series/DCOILWTICO</t>
+          <t>open data, redistributed with attribution</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X licence</t>
+          <t>X pulled</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
+        <is>
+          <t>26/09/2026 19:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>X steps</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>X raw sheet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>full series as pulled, before any transform</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Y label</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>US regular gasoline ($/gallon)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Y detail</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>US regular all formulations retail gasoline, $ per gallon, weekly averaged to monthly, FRED GASREGW, 08/1990 - present</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Y source</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FRED GASREGW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Y source URL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://fred.stlouisfed.org/series/GASREGW</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Y licence</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>open data, redistributed with attribution</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
-          <t>X pulled</t>
+          <t>Y pulled</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
-          <t>25/09/2026 02:03</t>
+          <t>26/09/2026 19:05</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
-          <t>X steps</t>
+          <t>Y steps</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
-          <t>X raw sheet</t>
+          <t>Y raw sheet</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>full series as pulled, before any transform</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
-          <t>Y label</t>
+          <t>join</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
-          <t>US regular gasoline ($/gallon)</t>
+          <t>resampled to M by mean</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
-          <t>Y detail</t>
+          <t>lag</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
-          <t>US regular all formulations retail gasoline, $ per gallon, weekly averaged to monthly, FRED GASREGW, 08/1990 - present</t>
+          <t>X leads Y by 0 periods</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
-          <t>Y source</t>
+          <t>transform</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>FRED GASREGW</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Y source URL</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>https://fred.stlouisfed.org/series/GASREGW</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Y licence</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>open data, redistributed with attribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Y pulled</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>25/09/2026 02:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Y steps</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Y raw sheet</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>full series as pulled, before any transform</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>join</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>resampled to M by mean</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>lag</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>X leads Y by 0 periods</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>p-value</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Newey-West (HAC) for time series</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>p-value</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Newey-West (HAC) for time series</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>correlation is not causation</t>
         </is>
